--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.25488244207504</v>
+        <v>5.566418396837194</v>
       </c>
       <c r="D2" t="n">
-        <v>33.56383102529539</v>
+        <v>5.4541225416105</v>
       </c>
       <c r="E2" t="n">
-        <v>6.38801263193801</v>
+        <v>1.038052052689927</v>
       </c>
       <c r="F2" t="n">
-        <v>6.116725156070462</v>
+        <v>0.9939678378614502</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.36187284990438</v>
+        <v>5.421304338109462</v>
       </c>
       <c r="D3" t="n">
-        <v>32.68711994867238</v>
+        <v>5.311656991659262</v>
       </c>
       <c r="E3" t="n">
-        <v>6.38801263193801</v>
+        <v>1.038052052689927</v>
       </c>
       <c r="F3" t="n">
-        <v>6.116725156070462</v>
+        <v>0.9939678378614502</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.49884530460581</v>
+        <v>4.306062361998444</v>
       </c>
       <c r="D4" t="n">
-        <v>25.78754994921708</v>
+        <v>4.190476866747776</v>
       </c>
       <c r="E4" t="n">
-        <v>6.38801263193801</v>
+        <v>1.038052052689927</v>
       </c>
       <c r="F4" t="n">
-        <v>6.116725156070462</v>
+        <v>0.9939678378614502</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.7390211656982</v>
+        <v>4.507590939425957</v>
       </c>
       <c r="D5" t="n">
-        <v>27.09689299901783</v>
+        <v>4.403245112340398</v>
       </c>
       <c r="E5" t="n">
-        <v>6.38801263193801</v>
+        <v>1.038052052689927</v>
       </c>
       <c r="F5" t="n">
-        <v>6.116725156070462</v>
+        <v>0.9939678378614502</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.04950685624003</v>
+        <v>4.720544864139004</v>
       </c>
       <c r="D6" t="n">
-        <v>28.44401488435799</v>
+        <v>4.622152418708174</v>
       </c>
       <c r="E6" t="n">
-        <v>6.38801263193801</v>
+        <v>1.038052052689927</v>
       </c>
       <c r="F6" t="n">
-        <v>6.116725156070462</v>
+        <v>0.9939678378614502</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.26987877647852</v>
+        <v>3.29385530117776</v>
       </c>
       <c r="D7" t="n">
-        <v>20.33650764627457</v>
+        <v>3.304682492519618</v>
       </c>
       <c r="E7" t="n">
-        <v>6.38801263193801</v>
+        <v>1.038052052689927</v>
       </c>
       <c r="F7" t="n">
-        <v>6.116725156070462</v>
+        <v>0.9939678378614502</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.82310356906586</v>
+        <v>5.333754329973202</v>
       </c>
       <c r="D8" t="n">
-        <v>32.84609032348454</v>
+        <v>5.337489677566237</v>
       </c>
       <c r="E8" t="n">
-        <v>6.38801263193801</v>
+        <v>1.038052052689927</v>
       </c>
       <c r="F8" t="n">
-        <v>6.116725156070462</v>
+        <v>0.9939678378614502</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.74893315095689</v>
+        <v>2.396701637030494</v>
       </c>
       <c r="D9" t="n">
-        <v>15.09426695194596</v>
+        <v>2.452818379691219</v>
       </c>
       <c r="E9" t="n">
-        <v>6.38801263193801</v>
+        <v>1.038052052689927</v>
       </c>
       <c r="F9" t="n">
-        <v>6.116725156070462</v>
+        <v>0.9939678378614502</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
